--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260604.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,334,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,334,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,12 +1723,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
